--- a/nop-seago/nop-seago-list/src/test/resources/_vfs/seago/po/test-import.xlsx
+++ b/nop-seago/nop-seago-list/src/test/resources/_vfs/seago/po/test-import.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12180"/>
+    <workbookView windowWidth="13404" windowHeight="4452"/>
   </bookViews>
   <sheets>
     <sheet name="TestEntity" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>唯一标识</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>所属部门</t>
+  </si>
+  <si>
+    <t>角色/等级</t>
   </si>
   <si>
     <t>姓名</t>
@@ -87,37 +90,31 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -579,163 +576,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1057,10 +1053,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1068,82 +1064,95 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D4">
         <v>24</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="D5">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>46</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D6">
         <v>34</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B1:E1"/>
+  <mergeCells count="5">
+    <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C1048576">
